--- a/vorpruefung_output_corrected.xlsx
+++ b/vorpruefung_output_corrected.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15B1E429-CFF1-48CA-A2DB-DD5D7F8958EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F593413A-9C3C-411F-A40C-29BB23F15262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28560" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21023,10 +21023,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:AS18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:45" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>226</v>
       </c>
@@ -21043,77 +21043,93 @@
         <v>318</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="AA2" t="str">
+        <f>_xlfn.VSTACK('III. Finanzberichte'!$B$41:$F$45,'III. Finanzberichte'!$I$41:$M$45,'III. Finanzberichte'!$P$41:$T$45,'III. Finanzberichte'!$W$41:$AA$45,'III. Finanzberichte'!$AD$41:$AH$45,'III. Finanzberichte'!$AK$41:$AO$45,'III. Finanzberichte'!$AR$41:$AV$45,'III. Finanzberichte'!$AY$41:$BC$45,'III. Finanzberichte'!$BF$41:$BJ$45,'III. Finanzberichte'!$BM$41:$BQ$45,'III. Finanzberichte'!$BT$41:$BX$45,'III. Finanzberichte'!$CA$41:$CE$45,'III. Finanzberichte'!$CH$41:$CL$45,'III. Finanzberichte'!$CO$41:$CS$45,'III. Finanzberichte'!$CV$41:$CZ$45,'III. Finanzberichte'!$DC$41:$DG$45,'III. Finanzberichte'!$DJ$41:$DN$45,'III. Finanzberichte'!$DQ$41:$DU$45)</f>
+        <v>Saldo des Vorprojekts</v>
+      </c>
+      <c r="AG2" t="str">
+        <f>_xlfn.VSTACK('III. Finanzberichte'!$B$50:$F$55,'III. Finanzberichte'!$I$50:$M$55,'III. Finanzberichte'!$P$50:$T$55,'III. Finanzberichte'!$W$50:$AA$55,'III. Finanzberichte'!$AD$50:$AH$55,'III. Finanzberichte'!$AK$50:$AO$55,'III. Finanzberichte'!$AR$50:$AV$55,'III. Finanzberichte'!$AY$50:$BC$55,'III. Finanzberichte'!$BF$50:$BJ$55,'III. Finanzberichte'!$BM$50:$BQ$55,'III. Finanzberichte'!$BT$50:$BX$55,'III. Finanzberichte'!$CA$50:$CE$55,'III. Finanzberichte'!$CH$50:$CL$55,'III. Finanzberichte'!$CO$50:$CS$55,'III. Finanzberichte'!$CV$50:$CZ$55,'III. Finanzberichte'!$DC$50:$DG$55,'III. Finanzberichte'!$DJ$50:$DN$55,'III. Finanzberichte'!$DQ$50:$DU$55)</f>
+        <v>Eigenmittel</v>
+      </c>
+      <c r="AM2" t="str">
+        <f ca="1">_xlfn.VSTACK('III. Finanzberichte'!$B$19:$F$26,'III. Finanzberichte'!$I$19:$M$26,'III. Finanzberichte'!$P$19:$T$26,'III. Finanzberichte'!$W$19:$AA$26,'III. Finanzberichte'!$AD$19:$AH$26,'III. Finanzberichte'!$AK$19:$AO$26,'III. Finanzberichte'!$AR$19:$AV$26,'III. Finanzberichte'!$AY$19:$BC$26,'III. Finanzberichte'!$BF$19:$BJ$26,'III. Finanzberichte'!$BM$19:$BQ$26,'III. Finanzberichte'!$BT$19:$BX$26,'III. Finanzberichte'!$CA$19:$CE$26,'III. Finanzberichte'!$CH$19:$CL$26,'III. Finanzberichte'!$CO$19:$CS$26,'III. Finanzberichte'!$CV$19:$CZ$26,'III. Finanzberichte'!$DC$19:$DG$26,'III. Finanzberichte'!$DJ$19:$DN$26,'III. Finanzberichte'!$DQ$19:$DU$26)</f>
+        <v/>
+      </c>
+      <c r="AS2" t="str">
+        <f>_xlfn.VSTACK('IV. MA'!$B$10:$D$17,'IV. MA'!$F$10:$H$17,'IV. MA'!$J$10:$L$17,'IV. MA'!$N$10:$P$17,'IV. MA'!$R$10:$T$17,'IV. MA'!$V$10:$X$17,'IV. MA'!$Z$10:$AB$17,'IV. MA'!$AD$10:$AF$17,'IV. MA'!$AH$10:$AJ$17,'IV. MA'!$AL$10:$AN$17,'IV. MA'!$AP$10:$AR$17,'IV. MA'!$AT$10:$AV$17,'IV. MA'!$AX$10:$AZ$17,'IV. MA'!$BB$10:$BD$17,'IV. MA'!$BF$10:$BH$17,'IV. MA'!$BJ$10:$BL$17,'IV. MA'!$BN$10:$BP$17,'IV. MA'!$BR$10:$BT$17)</f>
+        <v>Bauausgaben</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>241</v>
       </c>
